--- a/лаба.xlsx
+++ b/лаба.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Program Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6952BD71-93BD-4F10-8E9D-E5BF722A8AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A6A77B-44F7-482A-AA27-7E28336941E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Данные" sheetId="1" r:id="rId1"/>
@@ -9253,7 +9253,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D3" cm="1">
-        <f t="array" ref="D3">INDEX(Данные!C4:C63, MATCH(MAX(ABS(Данные!C4:C63)), ABS(Данные!C4:C63), 0))</f>
+        <f t="array" ref="D3">MAX(ABS(Данные!C4:C63))</f>
         <v>0</v>
       </c>
       <c r="E3" s="5" t="e">
@@ -9261,7 +9261,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="F3" cm="1">
-        <f t="array" ref="F3">INDEX(Данные!D4:D63, MATCH(MAX(ABS(Данные!D4:D63)), ABS(Данные!D4:D63), 0))</f>
+        <f t="array" ref="F3">MAX(ABS(Данные!D4:D63))</f>
         <v>0</v>
       </c>
       <c r="G3" s="5" t="e">
@@ -9327,7 +9327,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D4" cm="1">
-        <f t="array" ref="D4">INDEX(Данные!I4:I63, MATCH(MAX(ABS(Данные!I4:I63)), ABS(Данные!I4:I63), 0))</f>
+        <f t="array" ref="D4">MAX(ABS(Данные!I4:I63))</f>
         <v>0</v>
       </c>
       <c r="E4" s="5" t="e">
@@ -9335,7 +9335,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="F4" cm="1">
-        <f t="array" ref="F4">INDEX(Данные!J4:J63, MATCH(MAX(ABS(Данные!J4:J63)), ABS(Данные!J4:J63), 0))</f>
+        <f t="array" ref="F4">MAX(ABS(Данные!J4:J63))</f>
         <v>0</v>
       </c>
       <c r="G4" s="5" t="e">
@@ -9401,7 +9401,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D5" cm="1">
-        <f t="array" ref="D5">INDEX(Данные!O4:O63, MATCH(MAX(ABS(Данные!O4:O63)), ABS(Данные!O4:O63), 0))</f>
+        <f t="array" ref="D5">MAX(ABS(Данные!O4:O63))</f>
         <v>0</v>
       </c>
       <c r="E5" s="5" t="e">
@@ -9409,7 +9409,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="F5" cm="1">
-        <f t="array" ref="F5">INDEX(Данные!P4:P63, MATCH(MAX(ABS(Данные!P4:P63)), ABS(Данные!P4:P63), 0))</f>
+        <f t="array" ref="F5">MAX(ABS(Данные!P4:P63))</f>
         <v>0</v>
       </c>
       <c r="G5" s="5" t="e">
@@ -9475,7 +9475,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D6" cm="1">
-        <f t="array" ref="D6">INDEX(Данные!U4:U63, MATCH(MAX(ABS(Данные!U4:U63)), ABS(Данные!U4:U63), 0))</f>
+        <f t="array" ref="D6">MAX(ABS(Данные!U4:U63))</f>
         <v>0</v>
       </c>
       <c r="E6" s="5" t="e">
@@ -9483,7 +9483,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="F6" cm="1">
-        <f t="array" ref="F6">INDEX(Данные!V4:V63, MATCH(MAX(ABS(Данные!V4:V63)), ABS(Данные!V4:V63), 0))</f>
+        <f t="array" ref="F6">MAX(ABS(Данные!V4:V63))</f>
         <v>0</v>
       </c>
       <c r="G6" s="5" t="e">
@@ -9549,7 +9549,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D7" cm="1">
-        <f t="array" ref="D7">INDEX(Данные!AA4:AA63, MATCH(MAX(ABS(Данные!AA4:AA63)), ABS(Данные!AA4:AA63), 0))</f>
+        <f t="array" ref="D7">MAX(ABS(Данные!AA4:AA63))</f>
         <v>0</v>
       </c>
       <c r="E7" s="5" t="e">
@@ -9557,7 +9557,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="F7" cm="1">
-        <f t="array" ref="F7">INDEX(Данные!AB4:AB63, MATCH(MAX(ABS(Данные!AB4:AB63)), ABS(Данные!AB4:AB63), 0))</f>
+        <f t="array" ref="F7">MAX(ABS(Данные!AB4:AB63))</f>
         <v>0</v>
       </c>
       <c r="G7" s="5" t="e">
